--- a/bonus/bonus_points.xlsx
+++ b/bonus/bonus_points.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bonus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A69CD6-FD7F-0545-A4AB-FAB597F8521D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBD28A6-14B2-5849-BC23-2665218585D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="51">
   <si>
     <t>Season</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>2026</t>
+  </si>
+  <si>
+    <t>131</t>
   </si>
 </sst>
 </file>
@@ -1490,10 +1493,18 @@
       <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -1518,10 +1529,18 @@
       <c r="Z30" s="1"/>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -1546,10 +1565,18 @@
       <c r="Z31" s="1"/>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>

--- a/bonus/bonus_points.xlsx
+++ b/bonus/bonus_points.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bonus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBD28A6-14B2-5849-BC23-2665218585D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424242FD-82AB-E945-AEB2-DAE3DF45F239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="51">
   <si>
     <t>Season</t>
   </si>
@@ -1601,10 +1601,18 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>

--- a/bonus/bonus_points.xlsx
+++ b/bonus/bonus_points.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matevass/Documents/Programming/R/darts-statistics/bonus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424242FD-82AB-E945-AEB2-DAE3DF45F239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB82D97-53C4-1846-890B-BA0656099336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="52">
   <si>
     <t>Season</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>131</t>
+  </si>
+  <si>
+    <t>130</t>
   </si>
 </sst>
 </file>
@@ -1637,10 +1640,18 @@
       <c r="Z33" s="1"/>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
